--- a/OUT_EXCEL/out_7.xlsx
+++ b/OUT_EXCEL/out_7.xlsx
@@ -444,11 +444,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PRZESTRUCTURE</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -462,12 +458,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ODDS1IN</t>
+          <t>ODDS 1 IN:</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>#OF WINNERS*</t>
+          <t>#OF WINNERS'</t>
         </is>
       </c>
     </row>
@@ -477,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$3</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -497,7 +493,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$5</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -517,7 +513,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$7</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -537,7 +533,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$10</t>
+          <t>510</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -557,7 +553,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$20</t>
+          <t>520</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -577,7 +573,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$30</t>
+          <t>530</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -597,7 +593,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$50</t>
+          <t>550</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -637,7 +633,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$500</t>
+          <t>55oo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -657,7 +653,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>$40,000</t>
+          <t>540.000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -677,7 +673,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>[Total</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
